--- a/data/tags/אלבומים חדשים/global/2026-05-week04/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/2026-05-week04/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עומר אדם - אלבום הופעה איצטדיון רמת גן 2026</v>
+        <v>יוני רכטר – סגור פתוח סגור</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-28</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24471&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%99%d7%95%d7%a0%d7%99-%d7%a8%d7%9b%d7%98%d7%a8-%d7%a1%d7%92%d7%95%d7%a8-%d7%a4%d7%aa%d7%95%d7%97-%d7%a1%d7%92%d7%95%d7%a8/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>14:04</v>
+        <v>יוני רכטר לא הקליט אלבום אינסטרומנטלי מאז האלבום 'ממש עכשיו – מנגנים יוני רכטר' (1991). ההזדמנות להקליט אחד כזה פעם נוספת התאפשרה בעקבות הטריו שהקים לפני מספר שנים, שכולל מלבדו בפסנתר את נגן הקונטרבס ברק מורי והמתופפת רוני כספי. הקטע</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>עומר אדם - אלבום הופעה איצטדיון רמת גן 2026</v>
+        <v>יוני רכטר – סגור פתוח סגור</v>
       </c>
     </row>
   </sheetData>
